--- a/会员管理_QA测试问题清单.xlsx
+++ b/会员管理_QA测试问题清单.xlsx
@@ -11,7 +11,7 @@
     <sheet name="问题清单" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'问题清单'!$A$1:$L$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'问题清单'!$A$1:$L$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -621,7 +621,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>测试日期：2026-10-01　测试对象：content.html（巢状／压缩模式；正常／无数据／极限三种数据；1440／1024／768 宽度）</t>
+          <t>测试日期：2026-10-01（第1–2轮）、2026-10-02（第3轮：线上版 GitHub Pages）　测试对象：content.html（巢状／压缩模式；正常／无数据／极限三种数据；1440／1024／768 宽度）</t>
         </is>
       </c>
     </row>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('问题清单'!$E$2:$E$53,A5)</f>
+        <f>COUNTIF('问题清单'!$E$2:$E$78,A5)</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('问题清单'!$E$2:$E$53,A5,'问题清单'!$K$2:$K$53,"已修复")</f>
+        <f>COUNTIFS('问题清单'!$E$2:$E$78,A5,'问题清单'!$K$2:$K$78,"已修复")</f>
         <v/>
       </c>
       <c r="D5" s="5">
@@ -682,11 +682,11 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('问题清单'!$E$2:$E$53,A6)</f>
+        <f>COUNTIF('问题清单'!$E$2:$E$78,A6)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('问题清单'!$E$2:$E$53,A6,'问题清单'!$K$2:$K$53,"已修复")</f>
+        <f>COUNTIFS('问题清单'!$E$2:$E$78,A6,'问题清单'!$K$2:$K$78,"已修复")</f>
         <v/>
       </c>
       <c r="D6" s="5">
@@ -705,11 +705,11 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('问题清单'!$E$2:$E$53,A7)</f>
+        <f>COUNTIF('问题清单'!$E$2:$E$78,A7)</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('问题清单'!$E$2:$E$53,A7,'问题清单'!$K$2:$K$53,"已修复")</f>
+        <f>COUNTIFS('问题清单'!$E$2:$E$78,A7,'问题清单'!$K$2:$K$78,"已修复")</f>
         <v/>
       </c>
       <c r="D7" s="5">
@@ -778,15 +778,15 @@
         </is>
       </c>
       <c r="B11" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A11,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A11,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C11" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A11,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A11,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A11,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A11,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E11" s="5">
@@ -801,15 +801,15 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A12,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A12,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A12,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A12,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A12,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A12,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E12" s="5">
@@ -824,15 +824,15 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A13,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A13,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A13,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A13,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A13,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A13,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E13" s="5">
@@ -847,15 +847,15 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A14,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A14,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A14,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A14,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A14,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A14,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E14" s="5">
@@ -870,15 +870,15 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A15,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A15,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A15,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A15,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A15,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A15,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E15" s="5">
@@ -893,15 +893,15 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A16,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A16,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A16,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A16,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A16,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A16,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E16" s="5">
@@ -916,15 +916,15 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A17,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A17,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A17,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A17,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A17,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A17,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E17" s="5">
@@ -939,15 +939,15 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A18,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A18,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A18,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A18,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A18,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A18,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E18" s="5">
@@ -962,15 +962,15 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A19,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A19,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A19,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A19,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A19,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A19,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E19" s="5">
@@ -985,15 +985,15 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A20,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A20,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A20,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A20,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A20,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A20,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E20" s="5">
@@ -1008,15 +1008,15 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A21,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A21,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A21,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A21,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A21,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A21,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E21" s="5">
@@ -1031,15 +1031,15 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A22,'问题清单'!$E$2:$E$53,"高")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A22,'问题清单'!$E$2:$E$78,"高")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A22,'问题清单'!$E$2:$E$53,"中")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A22,'问题清单'!$E$2:$E$78,"中")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('问题清单'!$C$2:$C$53,$A22,'问题清单'!$E$2:$E$53,"低")</f>
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A22,'问题清单'!$E$2:$E$78,"低")</f>
         <v/>
       </c>
       <c r="E22" s="5">
@@ -1048,30 +1048,106 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>金额显示</t>
+        </is>
+      </c>
+      <c r="B23" s="5">
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A23,'问题清单'!$E$2:$E$78,"高")</f>
+        <v/>
+      </c>
+      <c r="C23" s="5">
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A23,'问题清单'!$E$2:$E$78,"中")</f>
+        <v/>
+      </c>
+      <c r="D23" s="5">
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A23,'问题清单'!$E$2:$E$78,"低")</f>
+        <v/>
+      </c>
+      <c r="E23" s="5">
+        <f>SUM(B23:D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>权限控制</t>
+        </is>
+      </c>
+      <c r="B24" s="5">
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A24,'问题清单'!$E$2:$E$78,"高")</f>
+        <v/>
+      </c>
+      <c r="C24" s="5">
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A24,'问题清单'!$E$2:$E$78,"中")</f>
+        <v/>
+      </c>
+      <c r="D24" s="5">
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A24,'问题清单'!$E$2:$E$78,"低")</f>
+        <v/>
+      </c>
+      <c r="E24" s="5">
+        <f>SUM(B24:D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>文案与用语</t>
+        </is>
+      </c>
+      <c r="B25" s="5">
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A25,'问题清单'!$E$2:$E$78,"高")</f>
+        <v/>
+      </c>
+      <c r="C25" s="5">
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A25,'问题清单'!$E$2:$E$78,"中")</f>
+        <v/>
+      </c>
+      <c r="D25" s="5">
+        <f>COUNTIFS('问题清单'!$C$2:$C$78,$A25,'问题清单'!$E$2:$E$78,"低")</f>
+        <v/>
+      </c>
+      <c r="E25" s="5">
+        <f>SUM(B25:D25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B23" s="10">
-        <f>SUM(B11:B22)</f>
-        <v/>
-      </c>
-      <c r="C23" s="10">
-        <f>SUM(C11:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="10">
-        <f>SUM(D11:D22)</f>
-        <v/>
-      </c>
-      <c r="E23" s="10">
-        <f>SUM(E11:E22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="B26" s="10">
+        <f>SUM(B11:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="10">
+        <f>SUM(C11:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="10">
+        <f>SUM(D11:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>SUM(E11:E25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>使用说明：在「问题清单」的「处理状态」栏选择状态（待处理／处理中／已修复／不修复／需确认），本页统计会自动更新。严重度定义：高＝结果错误或功能失效；中＝行为不一致或易误导；低＝无反应或 UI 细节。</t>
         </is>
@@ -1079,7 +1155,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A28:E28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1091,7 +1167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4225,9 +4301,1473 @@
       </c>
       <c r="L53" s="16" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>BUG-053</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>金额显示</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>巢状模式</t>
+        </is>
+      </c>
+      <c r="E54" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="inlineStr">
+        <is>
+          <t>「存取款（汇总 USDT）」不分币种一律除以 7.2</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>1. 正常数据、巢状模式
+2. 对照 vip_king（VND）与 test_user_4（USDT）的主钱包与汇总栏</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>VND 3,200 → 444.44 USDT；USDT 6,000.50 → 833.40 USDT；压缩模式又完全不换算，同一用户两种模式数值不同</t>
+        </is>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>依各币种汇率折算为 USDT（USDT 本身 1:1），两种模式一致</t>
+        </is>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1978-1980、851-852</t>
+        </is>
+      </c>
+      <c r="K54" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>BUG-054</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>金额显示</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="inlineStr">
+        <is>
+          <t>汇总后台加款／扣款写死为 0.00，展开卡片金额写死</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>1. 巢状模式查看 mingv0717001 的后台扣款总额
+2. 压缩模式展开同一列</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>主钱包显示「- RMB」，汇总却显示「0.00 USDT」；展开卡片固定显示后台加款 1,000,000、余额宝 15,000、利息 35</t>
+        </is>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>依用户实际资料显示；无数据时显示「-」</t>
+        </is>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1985-1986、2241-2286</t>
+        </is>
+      </c>
+      <c r="K55" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L55" s="16" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>BUG-055</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>金额显示</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>压缩模式</t>
+        </is>
+      </c>
+      <c r="E56" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="inlineStr">
+        <is>
+          <t>以「||」套预设值，真实的 0 被替换成假数字</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>1. 压缩模式查看 mingv0717001（balanceBuy＝0）的余额宝</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>显示 15,000（adminAdd 缺值时显示 200、利息显示 35）；对应排序也与画面数值不符</t>
+        </is>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>0 显示为 0，缺值显示「-」</t>
+        </is>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>script.js:3965、3972、3981-3982、4978</t>
+        </is>
+      </c>
+      <c r="K56" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L56" s="16" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>BUG-056</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>权限控制</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="inlineStr">
+        <is>
+          <t>「会员敏感资讯（手机）／（姓名）」等 11 个权限开关无作用</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>1. 左侧权限关闭「会员敏感资讯（姓名）」或「（手机）」
+2. 查看列表与详情</t>
+        </is>
+      </c>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>真实姓名、手机仍完整显示；查看会员列表、删除会员、RTP、赔率保存等 9 个权限也无任何对应处理</t>
+        </is>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>关闭后对应资讯遮罩或功能隐藏</t>
+        </is>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>content.html:1338-1550（无 TRACE_PERM_5A2F／B9EA／11FB／EB34／707E／A333／BB89／C694／8E6F／0919／25AC）</t>
+        </is>
+      </c>
+      <c r="K57" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L57" s="16" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>BUG-057</t>
+        </is>
+      </c>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>列表模式</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="inlineStr">
+        <is>
+          <t>查询结果为 0 笔时表头按钮全部失效</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>1. 精确账号输入 zzz 并搜寻
+2. 点表头右侧「自订栏位」图标／压缩模式排序、钉选</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>无任何反应</t>
+        </is>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>按钮正常运作</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1896-1903（提早 return，跳过 2324、2459-2487 事件绑定）</t>
+        </is>
+      </c>
+      <c r="K58" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L58" s="16" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>BUG-058</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>筛选与搜寻</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>筛选条件未按「搜寻」就生效，且筛选标签不同步</t>
+        </is>
+      </c>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>1. 「状态」选「冻结」但不点搜寻
+2. 翻页或切换压缩模式</t>
+        </is>
+      </c>
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>列表已只剩冻结会员，上方没有「状态: 冻结」标签</t>
+        </is>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>条件需点「搜寻」才套用；标签与实际条件一致</t>
+        </is>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>script.js:456-483、1509-1532</t>
+        </is>
+      </c>
+      <c r="K59" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L59" s="16" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="inlineStr">
+        <is>
+          <t>BUG-059</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>筛选与搜寻</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E60" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="inlineStr">
+        <is>
+          <t>点「搜寻」不会回到第 1 页</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>1. 翻到第 5 页
+2. 输入条件搜出 2 页结果</t>
+        </is>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>停在最后一页（第 2 页）</t>
+        </is>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>搜寻后回到第 1 页</t>
+        </is>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>script.js:2820-2827</t>
+        </is>
+      </c>
+      <c r="K60" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L60" s="16" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="inlineStr">
+        <is>
+          <t>BUG-060</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>用户抽屉</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="inlineStr">
+        <is>
+          <t>编辑用户保存时未校验栏位格式</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>1. 编辑用户，Email 填 not-an-email、手机填 abc
+2. 点「保存修改」</t>
+        </is>
+      </c>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>无任何错误提示，直接显示「用户详情已更新！」</t>
+        </is>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>显示格式错误提示并阻止保存（另见 BUG-008 未实际保存）</t>
+        </is>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>script.js:3478-3482</t>
+        </is>
+      </c>
+      <c r="K61" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L61" s="16" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="inlineStr">
+        <is>
+          <t>BUG-061</t>
+        </is>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>列表模式</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="E62" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="inlineStr">
+        <is>
+          <t>「离开天数」与最后登录时间不符</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>1. 对照 mingv0717001 与 mingv0717001_1（最后登录同为 2023-01-10 15:30）</t>
+        </is>
+      </c>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>分别显示 9天、10天；数值与日期无关</t>
+        </is>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>依最后登录时间计算</t>
+        </is>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1019（(offlineDays + i) % 15）</t>
+        </is>
+      </c>
+      <c r="K62" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L62" s="16" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="inlineStr">
+        <is>
+          <t>BUG-062</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>无数据状态</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="inlineStr">
+        <is>
+          <t>无数据时显示「N/A」，金额仍带单位</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>1. ?mock=nodata
+2. 查看会员名、真实姓名、备注与汇总栏、底部统计列</t>
+        </is>
+      </c>
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>显示「N/A」；汇总显示「- USDT」，统计列「- USDT」「- 人」</t>
+        </is>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>依 GEMINI.md 统一显示「-」，不带单位</t>
+        </is>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>script.js:792、1936-1938、1982-1986；content.html:349-364</t>
+        </is>
+      </c>
+      <c r="K63" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L63" s="16" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>BUG-063</t>
+        </is>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>无数据状态</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>无数据</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="inlineStr">
+        <is>
+          <t>「设备与IP纪录」页签整个被清空成「-」</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>1. ?mock=nodata
+2. 打开查看详情 → 设备与IP纪录</t>
+        </is>
+      </c>
+      <c r="H64" s="16" t="inlineStr">
+        <is>
+          <t>标题与栏位全部消失，只剩一个「-」</t>
+        </is>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>保留栏位结构，仅数值显示「-」</t>
+        </is>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>script.js:3204-3209（div 比对范围过大）</t>
+        </is>
+      </c>
+      <c r="K64" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L64" s="16" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>BUG-064</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>无数据状态</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>无数据 / 压缩模式</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F65" s="17" t="inlineStr">
+        <is>
+          <t>压缩模式「⋯」选单在无数据时仍可打开抽屉</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>1. ?mock=nodata 切压缩模式
+2. ⋯ → 编辑用户</t>
+        </is>
+      </c>
+      <c r="H65" s="16" t="inlineStr">
+        <is>
+          <t>抽屉照常打开（巢状模式会阻止）</t>
+        </is>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>两种模式行为一致</t>
+        </is>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>script.js:2389-2392 vs 3440</t>
+        </is>
+      </c>
+      <c r="K65" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L65" s="16" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>BUG-065</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>金额显示</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t>巢状模式</t>
+        </is>
+      </c>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>点「存款次数／取款次数」会弹出币种换算弹窗</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>1. 巢状模式点 vip_king 的「存款次数 8」</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="inlineStr">
+        <is>
+          <t>弹出币种换算，把次数当金额</t>
+        </is>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>次数不可点击，或打开次数明细</t>
+        </is>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1974-1975、1987-1988</t>
+        </is>
+      </c>
+      <c r="K66" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L66" s="16" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="inlineStr">
+        <is>
+          <t>BUG-066</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C67" s="16" t="inlineStr">
+        <is>
+          <t>列表模式</t>
+        </is>
+      </c>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>巢状模式</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>巢状模式「钉选栏位」无效</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>1. 巢状模式 → 自订栏位 → 钉选「标签」
+2. 横向卷动表格</t>
+        </is>
+      </c>
+      <c r="H67" s="16" t="inlineStr">
+        <is>
+          <t>该栏未固定</t>
+        </is>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>钉选栏位固定于左侧</t>
+        </is>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1690-1692、1921-1922、3776</t>
+        </is>
+      </c>
+      <c r="K67" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L67" s="16" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>BUG-067</t>
+        </is>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>自订栏位</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t>压缩模式</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>展开卡片「其他」区不受「已加入主表」控制</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>1. 自订栏位将「其他／备注」加入主表
+2. 展开任一列</t>
+        </is>
+      </c>
+      <c r="H68" s="16" t="inlineStr">
+        <is>
+          <t>备注同时出现在主表与卡片</t>
+        </is>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>加入主表后卡片中隐藏</t>
+        </is>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>script.js:2307-2310、50-53</t>
+        </is>
+      </c>
+      <c r="K68" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L68" s="16" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="inlineStr">
+        <is>
+          <t>BUG-068</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>自订栏位</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>重新加入的栏位眼睛图标状态错误</t>
+        </is>
+      </c>
+      <c r="G69" s="16" t="inlineStr">
+        <is>
+          <t>1. 「余额」加入主表 → 点眼睛隐藏 → 点 × 移除 → 再点 + 加入</t>
+        </is>
+      </c>
+      <c r="H69" s="16" t="inlineStr">
+        <is>
+          <t>栏位已显示，图标仍为「隐藏」</t>
+        </is>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>图标与实际显示一致</t>
+        </is>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>script.js:4664-4703（对比 5352）</t>
+        </is>
+      </c>
+      <c r="K69" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L69" s="16" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="inlineStr">
+        <is>
+          <t>BUG-069</t>
+        </is>
+      </c>
+      <c r="B70" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>文案与用语</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E70" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>介面出现繁体字「暱」</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>1. 查看列表「用户暱称」、编辑／详情抽屉</t>
+        </is>
+      </c>
+      <c r="H70" s="16" t="inlineStr">
+        <is>
+          <t>显示「暱称」，其他处为「昵称」</t>
+        </is>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>依 GEMINI.md 统一为简体「昵称」</t>
+        </is>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1938、3907；content.html:525、861</t>
+        </is>
+      </c>
+      <c r="K70" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L70" s="16" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="inlineStr">
+        <is>
+          <t>BUG-070</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>极限状态</t>
+        </is>
+      </c>
+      <c r="D71" s="16" t="inlineStr">
+        <is>
+          <t>极限</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>极限数据被生成逻辑覆盖，且 mock 有重复 uid</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr">
+        <is>
+          <t>1. ?mock=extreme 查看用户ID、等级、离开天数</t>
+        </is>
+      </c>
+      <c r="H71" s="16" t="inlineStr">
+        <is>
+          <t>uid 变成 uid_1、等级为「VIP会员」等短值、9999 天被 %15 改小；mock_data_extreme.js 第 3/4/5、7/8/9 笔 uid 重复</t>
+        </is>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>保留极限值以测试溢出</t>
+        </is>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1016-1022；mock_data_extreme.js</t>
+        </is>
+      </c>
+      <c r="K71" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L71" s="16" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>BUG-071</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>筛选与搜寻</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>数字筛选未校验、精确匹配不分大小写</t>
+        </is>
+      </c>
+      <c r="G72" s="16" t="inlineStr">
+        <is>
+          <t>1. 存款金额大于输入 abc、未登入天数输入 -5 并搜寻
+2. 账号（精确匹配）输入 VIP_KING</t>
+        </is>
+      </c>
+      <c r="H72" s="16" t="inlineStr">
+        <is>
+          <t>产生「存款大于 abc」等标签但筛选无效；VIP_KING 可查到 vip_king</t>
+        </is>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>限制数字输入并提示；精确匹配应区分大小写（需确认）</t>
+        </is>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1206、1531、1585</t>
+        </is>
+      </c>
+      <c r="K72" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L72" s="16" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>BUG-072</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>筛选与搜寻</t>
+        </is>
+      </c>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>新增时间结束只精确到分钟，边界记录被排除</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="inlineStr">
+        <is>
+          <t>1. 新增时间结束设 15:30
+2. 搜寻含 15:30:00 的记录</t>
+        </is>
+      </c>
+      <c r="H73" s="16" t="inlineStr">
+        <is>
+          <t>该笔被排除</t>
+        </is>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>结束时间包含整分钟（≤ 15:30:59）</t>
+        </is>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1579</t>
+        </is>
+      </c>
+      <c r="K73" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L73" s="16" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="inlineStr">
+        <is>
+          <t>BUG-073</t>
+        </is>
+      </c>
+      <c r="B74" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>弹窗与抽屉</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E74" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>showToast 定义两次，提示会挡住底部点击</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>1. 保存编辑后立即点底部区域</t>
+        </is>
+      </c>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>3 秒内 toast 挡住点击（后定义版本缺 pointer-events:none）</t>
+        </is>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>toast 不阻挡点击</t>
+        </is>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>script.js:3486 被 4828 覆盖</t>
+        </is>
+      </c>
+      <c r="K74" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L74" s="16" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>BUG-074</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>文案与用语</t>
+        </is>
+      </c>
+      <c r="D75" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>用语与语系标记不一致</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>1. 查看顶栏、筛选标签与 HTML 原始码</t>
+        </is>
+      </c>
+      <c r="H75" s="16" t="inlineStr">
+        <is>
+          <t>顶栏多出「uu」文字；标签「登入 IP」vs 栏位「登录IP」；lang="zh-TW"；搜寻／储存／资讯等台湾用语</t>
+        </is>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>用语统一为简体中文惯用语，lang="zh-CN"</t>
+        </is>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>index.html:2、412；content.html:2</t>
+        </is>
+      </c>
+      <c r="K75" s="15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="L75" s="16" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
+        <is>
+          <t>BUG-075</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>列表模式</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E76" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>底部统计列不随筛选结果变动</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="inlineStr">
+        <is>
+          <t>1. 搜寻无结果的账号（zzz）</t>
+        </is>
+      </c>
+      <c r="H76" s="16" t="inlineStr">
+        <is>
+          <t>统计列仍显示 41.25 USDT、25,818.78 USDT 等</t>
+        </is>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>若应反映筛选结果则同步更新；若为全平台统计请标示</t>
+        </is>
+      </c>
+      <c r="J76" s="16" t="inlineStr">
+        <is>
+          <t>content.html:349-364</t>
+        </is>
+      </c>
+      <c r="K76" s="15" t="inlineStr">
+        <is>
+          <t>需确认</t>
+        </is>
+      </c>
+      <c r="L76" s="16" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>BUG-076</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C77" s="16" t="inlineStr">
+        <is>
+          <t>金额显示</t>
+        </is>
+      </c>
+      <c r="D77" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>规格冲突：「获取失败」应显示图示还是「-」</t>
+        </is>
+      </c>
+      <c r="G77" s="16" t="inlineStr">
+        <is>
+          <t>对照 data_status.md 与 GEMINI.md</t>
+        </is>
+      </c>
+      <c r="H77" s="16" t="inlineStr">
+        <is>
+          <t>程式依 data_status.md 显示警示图示</t>
+        </is>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>确认以哪份规格为准</t>
+        </is>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>script.js:809-810</t>
+        </is>
+      </c>
+      <c r="K77" s="15" t="inlineStr">
+        <is>
+          <t>需确认</t>
+        </is>
+      </c>
+      <c r="L77" s="16" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="inlineStr">
+        <is>
+          <t>BUG-077</t>
+        </is>
+      </c>
+      <c r="B78" s="15" t="inlineStr">
+        <is>
+          <t>第3轮</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>筛选与搜寻</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="E78" s="15" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>「存款金额大于」直接比较不同币种原始数值</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>1. 存款金额大于输入 5000 并搜寻</t>
+        </is>
+      </c>
+      <c r="H78" s="16" t="inlineStr">
+        <is>
+          <t>test_user_6（VND 10,000）被列入</t>
+        </is>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>确认是否应先换算为同一币种再比较</t>
+        </is>
+      </c>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
+          <t>script.js:1585</t>
+        </is>
+      </c>
+      <c r="K78" s="15" t="inlineStr">
+        <is>
+          <t>需确认</t>
+        </is>
+      </c>
+      <c r="L78" s="16" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L53"/>
-  <conditionalFormatting sqref="E2:E53">
+  <autoFilter ref="A1:L78"/>
+  <conditionalFormatting sqref="E2:E78">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E2="高"</formula>
     </cfRule>
@@ -4238,16 +5778,16 @@
       <formula>$E2="低"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K53">
+  <conditionalFormatting sqref="K2:K78">
     <cfRule type="expression" priority="4" dxfId="3">
       <formula>$K2="已修复"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K2:K53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待处理,处理中,已修复,不修复,需确认"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2:E78" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
   </dataValidations>
